--- a/exports/SENSEX_full_report.xlsx
+++ b/exports/SENSEX_full_report.xlsx
@@ -5059,7 +5059,7 @@
         <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -7082,16 +7082,16 @@
         <v>71292.88</v>
       </c>
       <c r="E59" t="n">
-        <v>73450.12</v>
+        <v>73246.03</v>
       </c>
       <c r="F59" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G59" t="n">
         <v>4.93</v>
       </c>
       <c r="H59" t="n">
-        <v>1.74</v>
+        <v>1.46</v>
       </c>
       <c r="I59" t="n">
         <v>3.68</v>

--- a/exports/SENSEX_full_report.xlsx
+++ b/exports/SENSEX_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q81"/>
+  <dimension ref="A1:U81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>2.76</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44579.55208333334</v>
+        <v>44580.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>60755.64</v>
+        <v>60095.17</v>
       </c>
       <c r="I2" t="n">
         <v>60132.72458158044</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K2" t="n">
-        <v>0.83</v>
+        <v>-0.27</v>
       </c>
       <c r="L2" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="M2" t="n">
         <v>0.32</v>
       </c>
       <c r="N2" t="n">
-        <v>0.93</v>
+        <v>1.06</v>
       </c>
       <c r="O2" t="n">
         <v>1.04</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>2.89</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44593.55208333334</v>
+        <v>44594.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>58950.92</v>
+        <v>59443.09</v>
       </c>
       <c r="I3" t="n">
         <v>59119.44746273364</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K3" t="n">
-        <v>1.9</v>
+        <v>1.09</v>
       </c>
       <c r="L3" t="n">
         <v>1.26</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,28 +695,28 @@
         <v>4.21</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44603.55208333334</v>
+        <v>44606.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>58074.55</v>
+        <v>56994.18</v>
       </c>
       <c r="I4" t="n">
         <v>57250.45428010044</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.3</v>
+        <v>-4.12</v>
       </c>
       <c r="L4" t="n">
-        <v>4.01</v>
+        <v>4.76</v>
       </c>
       <c r="M4" t="n">
-        <v>0.73</v>
+        <v>2.33</v>
       </c>
       <c r="N4" t="n">
-        <v>1.68</v>
+        <v>3.01</v>
       </c>
       <c r="O4" t="n">
         <v>1.12</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S4" t="b">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -705,25 +764,25 @@
         <v>3.5</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44629.55208333334</v>
+        <v>44630.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>54733.31</v>
+        <v>55633.92</v>
       </c>
       <c r="I5" t="n">
         <v>55372.61727055326</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K5" t="n">
-        <v>3.97</v>
+        <v>2.39</v>
       </c>
       <c r="L5" t="n">
         <v>2.76</v>
       </c>
       <c r="M5" t="n">
-        <v>1.62</v>
+        <v>2.76</v>
       </c>
       <c r="N5" t="n">
         <v>3.24</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44616</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>4.85</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44662.55208333334</v>
+        <v>44663.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>58995.48</v>
+        <v>58381.74</v>
       </c>
       <c r="I6" t="n">
         <v>58787.89585229153</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K6" t="n">
-        <v>6.04</v>
+        <v>4.94</v>
       </c>
       <c r="L6" t="n">
         <v>1.17</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>2.95</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>54906.95</v>
+        <v>55976.34</v>
       </c>
       <c r="I7" t="n">
         <v>55023.88532582409</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>48</v>
       </c>
       <c r="K7" t="n">
-        <v>5.95</v>
+        <v>4.12</v>
       </c>
       <c r="L7" t="n">
         <v>1.06</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>3.74</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44721.55208333334</v>
+        <v>44722.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>55337.87</v>
+        <v>54362.88</v>
       </c>
       <c r="I8" t="n">
         <v>54693.50847656238</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.14</v>
+        <v>-2.88</v>
       </c>
       <c r="L8" t="n">
-        <v>2.62</v>
+        <v>2.92</v>
       </c>
       <c r="M8" t="n">
-        <v>0.58</v>
+        <v>1.04</v>
       </c>
       <c r="N8" t="n">
-        <v>1.03</v>
+        <v>1.94</v>
       </c>
       <c r="O8" t="n">
         <v>1.89</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,25 +1040,25 @@
         <v>3.41</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44736.55208333334</v>
+        <v>44739.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>52723.01</v>
+        <v>53354.51</v>
       </c>
       <c r="I9" t="n">
         <v>53115.61718014469</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K9" t="n">
-        <v>3.02</v>
+        <v>1.85</v>
       </c>
       <c r="L9" t="n">
         <v>0.76</v>
       </c>
       <c r="M9" t="n">
-        <v>0.93</v>
+        <v>1.41</v>
       </c>
       <c r="N9" t="n">
         <v>1.6</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>3.41</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44792.55208333334</v>
+        <v>44795.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>59548.49</v>
+        <v>58947.14</v>
       </c>
       <c r="I10" t="n">
         <v>59192.86694237943</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K10" t="n">
-        <v>11.61</v>
+        <v>10.48</v>
       </c>
       <c r="L10" t="n">
         <v>2.36</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>2.47</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44803.38541666666</v>
+        <v>44803.55208333334</v>
       </c>
       <c r="H11" t="n">
-        <v>59089.66</v>
+        <v>59503.63</v>
       </c>
       <c r="I11" t="n">
         <v>59466.2516071977</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.24</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>0.91</v>
+        <v>1.1</v>
       </c>
       <c r="M11" t="n">
         <v>0.52</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>3.22</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44819.55208333334</v>
+        <v>44820.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>59919.15</v>
+        <v>59037.84</v>
       </c>
       <c r="I12" t="n">
         <v>59395.34789749241</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>16</v>
+        <v>16.83333333333333</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7</v>
+        <v>-0.78</v>
       </c>
       <c r="L12" t="n">
         <v>1.64</v>
@@ -1125,7 +1268,7 @@
         <v>1.9</v>
       </c>
       <c r="N12" t="n">
-        <v>1.11</v>
+        <v>1.74</v>
       </c>
       <c r="O12" t="n">
         <v>2.5</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,19 +1316,19 @@
         <v>3.22</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44838.55208333334</v>
+        <v>44840.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>58079.92</v>
+        <v>58477.25</v>
       </c>
       <c r="I13" t="n">
         <v>58286.89480862307</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K13" t="n">
-        <v>1.62</v>
+        <v>0.95</v>
       </c>
       <c r="L13" t="n">
         <v>1.81</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>3.32</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44903.55208333334</v>
+        <v>44904.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>62574.69</v>
+        <v>62149.49</v>
       </c>
       <c r="I14" t="n">
         <v>62309.05688803222</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>63.16666666666666</v>
+        <v>64</v>
       </c>
       <c r="K14" t="n">
-        <v>7.01</v>
+        <v>6.28</v>
       </c>
       <c r="L14" t="n">
         <v>2.44</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>87</v>
+        <v>88</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>2.13</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44960.38541666666</v>
+        <v>44960.55208333334</v>
       </c>
       <c r="H15" t="n">
-        <v>60416.56</v>
+        <v>60801.27</v>
       </c>
       <c r="I15" t="n">
         <v>60595.0436552906</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K15" t="n">
-        <v>2.79</v>
+        <v>2.17</v>
       </c>
       <c r="L15" t="n">
         <v>1.1</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3</v>
+      </c>
+      <c r="U15" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>3.63</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>60703.39</v>
+        <v>59967.42</v>
       </c>
       <c r="I16" t="n">
         <v>60324.87534786292</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.16</v>
+        <v>-1.37</v>
       </c>
       <c r="L16" t="n">
-        <v>1.21</v>
+        <v>1.4</v>
       </c>
       <c r="M16" t="n">
-        <v>0.41</v>
+        <v>0.51</v>
       </c>
       <c r="N16" t="n">
-        <v>0.49</v>
+        <v>1.54</v>
       </c>
       <c r="O16" t="n">
         <v>1.45</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>2.44</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44988.55208333334</v>
+        <v>44991.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>59791.12</v>
+        <v>60422.16</v>
       </c>
       <c r="I17" t="n">
         <v>60071.94741057246</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K17" t="n">
-        <v>0.29</v>
+        <v>-0.76</v>
       </c>
       <c r="L17" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="M17" t="n">
         <v>0.5600000000000001</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,28 +1661,28 @@
         <v>2.43</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>59175.57</v>
+        <v>58630.99</v>
       </c>
       <c r="I18" t="n">
         <v>59071.37977442341</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K18" t="n">
-        <v>-2.06</v>
+        <v>-2.96</v>
       </c>
       <c r="L18" t="n">
-        <v>2.54</v>
+        <v>3.03</v>
       </c>
       <c r="M18" t="n">
         <v>0.88</v>
       </c>
       <c r="N18" t="n">
-        <v>1.02</v>
+        <v>1.34</v>
       </c>
       <c r="O18" t="n">
         <v>0.79</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>3.16</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45016.38541666666</v>
+        <v>45016.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>58799.01</v>
+        <v>58979.76</v>
       </c>
       <c r="I19" t="n">
         <v>58955.89231203283</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.29</v>
+        <v>-0.59</v>
       </c>
       <c r="L19" t="n">
         <v>1.5</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>2.41</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45062.55208333334</v>
+        <v>45063.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>61915.88</v>
+        <v>61384.83</v>
       </c>
       <c r="I20" t="n">
         <v>61441.15981016579</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>46</v>
+        <v>46.83333333333334</v>
       </c>
       <c r="K20" t="n">
-        <v>4.98</v>
+        <v>4.08</v>
       </c>
       <c r="L20" t="n">
         <v>0.33</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>2.24</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45072.55208333334</v>
+        <v>45075.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>62500.96</v>
+        <v>62846.89</v>
       </c>
       <c r="I21" t="n">
         <v>62515.37792475762</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.82</v>
+        <v>-2.38</v>
       </c>
       <c r="L21" t="n">
-        <v>1.87</v>
+        <v>2.67</v>
       </c>
       <c r="M21" t="n">
         <v>0.52</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>1.63</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45134.55208333334</v>
+        <v>45135.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>66409.39999999999</v>
+        <v>66029.31</v>
       </c>
       <c r="I22" t="n">
         <v>66292.09528578639</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>59.16666666666666</v>
+        <v>60</v>
       </c>
       <c r="K22" t="n">
-        <v>5.67</v>
+        <v>5.06</v>
       </c>
       <c r="L22" t="n">
         <v>0.77</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>86</v>
+        <v>87</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>2.12</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45175.38541666666</v>
+        <v>45175.55208333334</v>
       </c>
       <c r="H23" t="n">
-        <v>65552.45</v>
+        <v>65904.32000000001</v>
       </c>
       <c r="I23" t="n">
         <v>65864.36671273394</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>40</v>
+        <v>40.16666666666666</v>
       </c>
       <c r="K23" t="n">
-        <v>0.72</v>
+        <v>0.19</v>
       </c>
       <c r="L23" t="n">
         <v>0.95</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>1.71</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45189.38541666666</v>
+        <v>45189.55208333334</v>
       </c>
       <c r="H24" t="n">
-        <v>66909.84</v>
+        <v>66844.11</v>
       </c>
       <c r="I24" t="n">
         <v>66853.59537640204</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>13.83333333333333</v>
+        <v>14</v>
       </c>
       <c r="K24" t="n">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="L24" t="n">
         <v>0.63</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>1.41</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45209.55208333334</v>
+        <v>45210.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>66103.56</v>
+        <v>66487.47</v>
       </c>
       <c r="I25" t="n">
         <v>66248.63016414161</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K25" t="n">
-        <v>1.11</v>
+        <v>0.53</v>
       </c>
       <c r="L25" t="n">
         <v>0.11</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>2</v>
+      </c>
+      <c r="U25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
@@ -1902,22 +2213,22 @@
         <v>1.72</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45218.55208333334</v>
+        <v>45219.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>65600.94</v>
+        <v>65389.1</v>
       </c>
       <c r="I26" t="n">
         <v>65545.00921207397</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.33</v>
+        <v>-1.65</v>
       </c>
       <c r="L26" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="M26" t="n">
         <v>0.6</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,25 +2282,25 @@
         <v>1.61</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45233.55208333334</v>
+        <v>45236.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>64347.86</v>
+        <v>64780.44</v>
       </c>
       <c r="I27" t="n">
         <v>64498.42022498747</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K27" t="n">
-        <v>1.59</v>
+        <v>0.93</v>
       </c>
       <c r="L27" t="n">
         <v>0.25</v>
       </c>
       <c r="M27" t="n">
-        <v>0.66</v>
+        <v>0.76</v>
       </c>
       <c r="N27" t="n">
         <v>1.09</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>1.9</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45280.38541666666</v>
+        <v>45280.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>71500.60000000001</v>
+        <v>70359.62</v>
       </c>
       <c r="I28" t="n">
         <v>70466.54649749413</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>44</v>
+        <v>44.16666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>10.37</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="L28" t="n">
         <v>0.31</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>62</v>
+        <v>63</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>2</v>
+      </c>
+      <c r="U28" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>2.86</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45287.38541666666</v>
+        <v>45287.55208333334</v>
       </c>
       <c r="H29" t="n">
-        <v>71634.25999999999</v>
+        <v>72011.31</v>
       </c>
       <c r="I29" t="n">
         <v>71994.75453702976</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K29" t="n">
-        <v>-1.81</v>
+        <v>-2.35</v>
       </c>
       <c r="L29" t="n">
-        <v>2.15</v>
+        <v>2.5</v>
       </c>
       <c r="M29" t="n">
         <v>0.15</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>2.26</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45307.55208333334</v>
+        <v>45308.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>73119.99000000001</v>
+        <v>71702.84</v>
       </c>
       <c r="I30" t="n">
         <v>71932.794517869</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K30" t="n">
-        <v>1.54</v>
+        <v>-0.43</v>
       </c>
       <c r="L30" t="n">
         <v>1.25</v>
       </c>
       <c r="M30" t="n">
-        <v>0.06</v>
+        <v>1.53</v>
       </c>
       <c r="N30" t="n">
-        <v>0.9</v>
+        <v>2.22</v>
       </c>
       <c r="O30" t="n">
         <v>0.88</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>2.72</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45337.55208333334</v>
+        <v>45338.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>72091.53</v>
+        <v>72449.75</v>
       </c>
       <c r="I31" t="n">
         <v>72269.28811735997</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.54</v>
+        <v>-1.04</v>
       </c>
       <c r="L31" t="n">
         <v>1.93</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>2.33</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45364.38541666666</v>
+        <v>45364.55208333334</v>
       </c>
       <c r="H32" t="n">
-        <v>73086.60000000001</v>
+        <v>72737.34</v>
       </c>
       <c r="I32" t="n">
         <v>72769.05586209251</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>26</v>
+        <v>26.16666666666667</v>
       </c>
       <c r="K32" t="n">
-        <v>0.88</v>
+        <v>0.4</v>
       </c>
       <c r="L32" t="n">
         <v>0.51</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,28 +2696,28 @@
         <v>2.31</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45378.55208333334</v>
+        <v>45379.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>73032.95</v>
+        <v>73894.17</v>
       </c>
       <c r="I33" t="n">
         <v>73547.17443306236</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.41</v>
+        <v>-1.59</v>
       </c>
       <c r="L33" t="n">
-        <v>0.86</v>
+        <v>1.71</v>
       </c>
       <c r="M33" t="n">
         <v>0.49</v>
       </c>
       <c r="N33" t="n">
-        <v>0.77</v>
+        <v>0.82</v>
       </c>
       <c r="O33" t="n">
         <v>-1.23</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,28 +2765,28 @@
         <v>2.55</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45394.55208333334</v>
+        <v>45397.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>74228.42999999999</v>
+        <v>73625.52</v>
       </c>
       <c r="I34" t="n">
         <v>73841.20339981453</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K34" t="n">
-        <v>0.45</v>
+        <v>-0.36</v>
       </c>
       <c r="L34" t="n">
         <v>1.05</v>
       </c>
       <c r="M34" t="n">
-        <v>0.25</v>
+        <v>1.23</v>
       </c>
       <c r="N34" t="n">
-        <v>1.03</v>
+        <v>1.14</v>
       </c>
       <c r="O34" t="n">
         <v>0.82</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>1.85</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45405.55208333334</v>
+        <v>45406.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>73744.75999999999</v>
+        <v>74006.78</v>
       </c>
       <c r="I35" t="n">
         <v>73948.03973291878</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.16</v>
+        <v>-0.52</v>
       </c>
       <c r="L35" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="M35" t="n">
         <v>0.78</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S35" t="b">
+        <v>0</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1</v>
+      </c>
+      <c r="U35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -2472,22 +2903,22 @@
         <v>1.99</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>73947.03</v>
+        <v>73324.85000000001</v>
       </c>
       <c r="I36" t="n">
         <v>73473.97954423942</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.08</v>
+        <v>-0.92</v>
       </c>
       <c r="L36" t="n">
-        <v>0.73</v>
+        <v>1.01</v>
       </c>
       <c r="M36" t="n">
         <v>0.4</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>2.7</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45428.55208333334</v>
+        <v>45429.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>73638.13</v>
+        <v>73948.41</v>
       </c>
       <c r="I37" t="n">
         <v>73884.4620822124</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.43</v>
+        <v>-0.85</v>
       </c>
       <c r="L37" t="n">
         <v>0.96</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>2.63</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45441.55208333334</v>
+        <v>45442.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>74501.84</v>
+        <v>74146.11</v>
       </c>
       <c r="I38" t="n">
         <v>74233.21364429599</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K38" t="n">
-        <v>0.75</v>
+        <v>0.27</v>
       </c>
       <c r="L38" t="n">
         <v>0.66</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>2.09</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45443.55208333334</v>
+        <v>45446.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>74018.06</v>
+        <v>76269.95</v>
       </c>
       <c r="I39" t="n">
         <v>75358.00052583152</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K39" t="n">
-        <v>0.17</v>
+        <v>-2.86</v>
       </c>
       <c r="L39" t="n">
-        <v>0.47</v>
+        <v>3.5</v>
       </c>
       <c r="M39" t="n">
-        <v>0.15</v>
+        <v>3.47</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="O39" t="n">
         <v>-0.54</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>2.91</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>76599.09</v>
+        <v>72287.2</v>
       </c>
       <c r="I40" t="n">
         <v>74238.50186650193</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K40" t="n">
-        <v>0.43</v>
+        <v>-5.22</v>
       </c>
       <c r="L40" t="n">
-        <v>0.78</v>
+        <v>7.91</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>0.41</v>
       </c>
       <c r="N40" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="O40" t="n">
         <v>3.49</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>6.62</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>75167.25</v>
+        <v>76474.36</v>
       </c>
       <c r="I41" t="n">
         <v>76342.38428813344</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>3</v>
       </c>
       <c r="K41" t="n">
-        <v>-3.98</v>
+        <v>-5.79</v>
       </c>
       <c r="L41" t="n">
-        <v>5.55</v>
+        <v>5.95</v>
       </c>
       <c r="M41" t="n">
         <v>1.14</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>5.98</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45495.55208333334</v>
+        <v>45496.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>80518.74000000001</v>
+        <v>79768.67999999999</v>
       </c>
       <c r="I42" t="n">
         <v>79939.20610280955</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>45.16666666666666</v>
+        <v>46</v>
       </c>
       <c r="K42" t="n">
-        <v>5.29</v>
+        <v>4.31</v>
       </c>
       <c r="L42" t="n">
         <v>2</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>2.46</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45502.55208333334</v>
+        <v>45503.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>81363.11</v>
+        <v>81699.22</v>
       </c>
       <c r="I43" t="n">
         <v>81623.65122533041</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K43" t="n">
-        <v>-2</v>
+        <v>-2.42</v>
       </c>
       <c r="L43" t="n">
         <v>2.68</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>2.41</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45506.55208333334</v>
+        <v>45509.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>80924.89</v>
+        <v>78656.34</v>
       </c>
       <c r="I44" t="n">
         <v>80393.91632361099</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.95</v>
+        <v>-3.72</v>
       </c>
       <c r="L44" t="n">
-        <v>1.02</v>
+        <v>4.17</v>
       </c>
       <c r="M44" t="n">
-        <v>0.87</v>
+        <v>2.89</v>
       </c>
       <c r="N44" t="n">
-        <v>1.16</v>
+        <v>2.66</v>
       </c>
       <c r="O44" t="n">
         <v>0.06</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>3.23</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45523.55208333334</v>
+        <v>45524.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>80444.25999999999</v>
+        <v>80909.84</v>
       </c>
       <c r="I45" t="n">
         <v>80777.92956514179</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.27</v>
+        <v>-2.86</v>
       </c>
       <c r="L45" t="n">
-        <v>2.63</v>
+        <v>2.91</v>
       </c>
       <c r="M45" t="n">
         <v>1.41</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>2.2</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>82158.53</v>
+        <v>81219.17</v>
       </c>
       <c r="I46" t="n">
         <v>81533.7607731765</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K46" t="n">
-        <v>1.54</v>
+        <v>0.38</v>
       </c>
       <c r="L46" t="n">
         <v>0.48</v>
@@ -3063,7 +3614,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="N46" t="n">
-        <v>0.29</v>
+        <v>1.08</v>
       </c>
       <c r="O46" t="n">
         <v>0.33</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>2.14</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45547.38541666666</v>
+        <v>45547.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>81683.35000000001</v>
+        <v>82749.67999999999</v>
       </c>
       <c r="I47" t="n">
         <v>82378.8919226873</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>6</v>
+        <v>6.166666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.57</v>
+        <v>-1.88</v>
       </c>
       <c r="L47" t="n">
-        <v>1.28</v>
+        <v>2.34</v>
       </c>
       <c r="M47" t="n">
         <v>0.42</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>2.44</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45565.55208333334</v>
+        <v>45566.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>84362.52</v>
+        <v>84276.45</v>
       </c>
       <c r="I48" t="n">
         <v>84339.78018035326</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K48" t="n">
-        <v>1.95</v>
+        <v>1.85</v>
       </c>
       <c r="L48" t="n">
         <v>1.34</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,25 +3800,25 @@
         <v>1.91</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45618.55208333334</v>
+        <v>45621.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>78957.42999999999</v>
+        <v>79907.23</v>
       </c>
       <c r="I49" t="n">
         <v>79093.49881108606</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>52.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K49" t="n">
-        <v>6.31</v>
+        <v>5.18</v>
       </c>
       <c r="L49" t="n">
         <v>0.44</v>
       </c>
       <c r="M49" t="n">
-        <v>0.62</v>
+        <v>1.57</v>
       </c>
       <c r="N49" t="n">
         <v>2.36</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,25 +3869,25 @@
         <v>2.81</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45644.55208333334</v>
+        <v>45645.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>80231.83</v>
+        <v>79299.95</v>
       </c>
       <c r="I50" t="n">
         <v>80090.44361826782</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K50" t="n">
-        <v>0.41</v>
+        <v>-0.76</v>
       </c>
       <c r="L50" t="n">
         <v>1.24</v>
       </c>
       <c r="M50" t="n">
-        <v>0.23</v>
+        <v>1.5</v>
       </c>
       <c r="N50" t="n">
         <v>1.35</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>2.29</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45658.55208333334</v>
+        <v>45659.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>78581.23</v>
+        <v>79623.83</v>
       </c>
       <c r="I51" t="n">
         <v>79471.75432679889</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K51" t="n">
-        <v>0.91</v>
+        <v>-0.41</v>
       </c>
       <c r="L51" t="n">
-        <v>0.36</v>
+        <v>0.45</v>
       </c>
       <c r="M51" t="n">
         <v>0.35</v>
       </c>
       <c r="N51" t="n">
-        <v>0.45</v>
+        <v>1.68</v>
       </c>
       <c r="O51" t="n">
         <v>-1.23</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>2.86</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45663.38541666666</v>
+        <v>45663.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>78283.27</v>
+        <v>78014.27</v>
       </c>
       <c r="I52" t="n">
         <v>78121.46571411852</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-1.68</v>
+        <v>-2.02</v>
       </c>
       <c r="L52" t="n">
-        <v>2.09</v>
+        <v>2.31</v>
       </c>
       <c r="M52" t="n">
         <v>0.01</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>2.57</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45687.55208333334</v>
+        <v>45688.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>76887.85000000001</v>
+        <v>77460.53</v>
       </c>
       <c r="I53" t="n">
         <v>77135.67191163792</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>24</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>1.44</v>
+        <v>0.71</v>
       </c>
       <c r="L53" t="n">
         <v>0.5600000000000001</v>
@@ -3462,7 +4097,7 @@
         <v>0.71</v>
       </c>
       <c r="N53" t="n">
-        <v>0.82</v>
+        <v>0.88</v>
       </c>
       <c r="O53" t="n">
         <v>-1.46</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,28 +4145,28 @@
         <v>2.63</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45698.55208333334</v>
+        <v>45699.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>77302.21000000001</v>
+        <v>76189.53999999999</v>
       </c>
       <c r="I54" t="n">
         <v>76767.04323308526</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.2</v>
+        <v>-1.64</v>
       </c>
       <c r="L54" t="n">
-        <v>0.91</v>
+        <v>1.66</v>
       </c>
       <c r="M54" t="n">
         <v>0.67</v>
       </c>
       <c r="N54" t="n">
-        <v>0.7</v>
+        <v>1.3</v>
       </c>
       <c r="O54" t="n">
         <v>0.88</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>3.14</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45723.55208333334</v>
+        <v>45726.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>74308.99000000001</v>
+        <v>74553.03999999999</v>
       </c>
       <c r="I55" t="n">
         <v>74378.76281328133</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K55" t="n">
-        <v>2.47</v>
+        <v>2.15</v>
       </c>
       <c r="L55" t="n">
         <v>1.57</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>2.2</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45744.55208333334</v>
+        <v>45748.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>77344.47</v>
+        <v>76127.73</v>
       </c>
       <c r="I56" t="n">
         <v>76692.42303649777</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K56" t="n">
-        <v>3.74</v>
+        <v>2.11</v>
       </c>
       <c r="L56" t="n">
         <v>1.28</v>
       </c>
       <c r="M56" t="n">
-        <v>0.41</v>
+        <v>0.6</v>
       </c>
       <c r="N56" t="n">
-        <v>0.67</v>
+        <v>1.6</v>
       </c>
       <c r="O56" t="n">
         <v>-0.35</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>3.23</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45756.55208333334</v>
+        <v>45758.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>73898.12</v>
+        <v>75395.31</v>
       </c>
       <c r="I57" t="n">
         <v>74935.58223210178</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K57" t="n">
-        <v>2.93</v>
+        <v>0.96</v>
       </c>
       <c r="L57" t="n">
         <v>1.79</v>
       </c>
       <c r="M57" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.27</v>
       </c>
       <c r="N57" t="n">
-        <v>1.29</v>
+        <v>1.8</v>
       </c>
       <c r="O57" t="n">
         <v>-1.6</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,25 +4421,25 @@
         <v>4.06</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45820.55208333334</v>
+        <v>45821.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>81646.78999999999</v>
+        <v>81038.74000000001</v>
       </c>
       <c r="I58" t="n">
         <v>81203.7734844894</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>62.16666666666666</v>
+        <v>63</v>
       </c>
       <c r="K58" t="n">
-        <v>8.289999999999999</v>
+        <v>7.49</v>
       </c>
       <c r="L58" t="n">
         <v>0.84</v>
       </c>
       <c r="M58" t="n">
-        <v>1.29</v>
+        <v>1.49</v>
       </c>
       <c r="N58" t="n">
         <v>1.47</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>3</v>
+      </c>
+      <c r="U58" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>1.75</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45831.55208333334</v>
+        <v>45832.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>81860.73</v>
+        <v>82566.91</v>
       </c>
       <c r="I59" t="n">
         <v>82456.86568480723</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K59" t="n">
-        <v>-1.01</v>
+        <v>-1.89</v>
       </c>
       <c r="L59" t="n">
-        <v>1.8</v>
+        <v>2.44</v>
       </c>
       <c r="M59" t="n">
-        <v>0.14</v>
+        <v>0.82</v>
       </c>
       <c r="N59" t="n">
         <v>1.33</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,28 +4559,28 @@
         <v>1.93</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>83152.17999999999</v>
+        <v>82513.2</v>
       </c>
       <c r="I60" t="n">
         <v>82542.90384378309</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K60" t="n">
-        <v>0.71</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="L60" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="M60" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="N60" t="n">
-        <v>0.52</v>
+        <v>0.84</v>
       </c>
       <c r="O60" t="n">
         <v>0.37</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>2</v>
+      </c>
+      <c r="U60" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>1.78</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45883.55208333334</v>
+        <v>45887.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>80547.36</v>
+        <v>81507.47</v>
       </c>
       <c r="I61" t="n">
         <v>81476.69246580151</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>38</v>
       </c>
       <c r="K61" t="n">
-        <v>2.38</v>
+        <v>1.22</v>
       </c>
       <c r="L61" t="n">
         <v>0.64</v>
       </c>
       <c r="M61" t="n">
-        <v>0.36</v>
+        <v>0.95</v>
       </c>
       <c r="N61" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="O61" t="n">
         <v>-0.84</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>1.86</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45895.38541666666</v>
+        <v>45895.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>81094.3</v>
+        <v>80820.08</v>
       </c>
       <c r="I62" t="n">
         <v>80855.40898852095</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>-0.51</v>
+        <v>-0.84</v>
       </c>
       <c r="L62" t="n">
-        <v>0.7</v>
+        <v>1.01</v>
       </c>
       <c r="M62" t="n">
         <v>0.35</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>1.72</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45909.55208333334</v>
+        <v>45910.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>81107.03999999999</v>
+        <v>81406.89</v>
       </c>
       <c r="I63" t="n">
         <v>81340.17933104125</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-0.36</v>
+        <v>-0.73</v>
       </c>
       <c r="L63" t="n">
-        <v>0.79</v>
+        <v>1.02</v>
       </c>
       <c r="M63" t="n">
         <v>1.13</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>1.52</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45924.38541666666</v>
+        <v>45924.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>81947.00999999999</v>
+        <v>81739.92999999999</v>
       </c>
       <c r="I64" t="n">
         <v>81926.63531929679</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>0.66</v>
+        <v>0.41</v>
       </c>
       <c r="L64" t="n">
         <v>0.23</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,19 +4904,19 @@
         <v>1.54</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45933.55208333334</v>
+        <v>45936.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>81196.89999999999</v>
+        <v>81761.50999999999</v>
       </c>
       <c r="I65" t="n">
         <v>81623.27291653946</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>9</v>
+        <v>11.83333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>0.66</v>
+        <v>-0.03</v>
       </c>
       <c r="L65" t="n">
         <v>0.29</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>2.01</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45965.38541666666</v>
+        <v>45965.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>83682.53</v>
+        <v>83451.75</v>
       </c>
       <c r="I66" t="n">
         <v>83481.68266883471</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>29</v>
+        <v>29.16666666666667</v>
       </c>
       <c r="K66" t="n">
-        <v>2.35</v>
+        <v>2.07</v>
       </c>
       <c r="L66" t="n">
         <v>0.74</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S66" t="b">
+        <v>1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>2</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>1.75</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>83899.78</v>
+        <v>84634.16</v>
       </c>
       <c r="I67" t="n">
         <v>84354.14115766677</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>7</v>
+        <v>7.833333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>-0.54</v>
+        <v>-1.42</v>
       </c>
       <c r="L67" t="n">
-        <v>0.58</v>
+        <v>1.43</v>
       </c>
       <c r="M67" t="n">
-        <v>0.19</v>
+        <v>0.4</v>
       </c>
       <c r="N67" t="n">
-        <v>0.46</v>
+        <v>0.63</v>
       </c>
       <c r="O67" t="n">
         <v>-0.66</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,19 +5111,19 @@
         <v>1.97</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46000.55208333334</v>
+        <v>46001.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>84686.94</v>
+        <v>84497.14</v>
       </c>
       <c r="I68" t="n">
         <v>84533.69744777627</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K68" t="n">
-        <v>0.06</v>
+        <v>-0.16</v>
       </c>
       <c r="L68" t="n">
         <v>0.71</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,19 +5180,19 @@
         <v>1.88</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46023.55208333334</v>
+        <v>46024.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>85172.11</v>
+        <v>85657.53</v>
       </c>
       <c r="I69" t="n">
         <v>85636.15131922002</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>22.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K69" t="n">
-        <v>-0.8</v>
+        <v>-1.37</v>
       </c>
       <c r="L69" t="n">
         <v>1.47</v>
@@ -4374,7 +5201,7 @@
         <v>0.33</v>
       </c>
       <c r="N69" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="O69" t="n">
         <v>-0.37</v>
@@ -4383,7 +5210,19 @@
         <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,28 +5249,28 @@
         <v>1.6</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46029.55208333334</v>
+        <v>46030.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>84968.05</v>
+        <v>84329.09</v>
       </c>
       <c r="I70" t="n">
         <v>84627.64057929144</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K70" t="n">
-        <v>-0.8</v>
+        <v>-1.55</v>
       </c>
       <c r="L70" t="n">
-        <v>1.21</v>
+        <v>1.67</v>
       </c>
       <c r="M70" t="n">
         <v>0.48</v>
       </c>
       <c r="N70" t="n">
-        <v>0.48</v>
+        <v>0.95</v>
       </c>
       <c r="O70" t="n">
         <v>0.75</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S70" t="b">
+        <v>0</v>
+      </c>
+      <c r="T70" t="n">
+        <v>1</v>
+      </c>
+      <c r="U70" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -4467,28 +5318,28 @@
         <v>1.71</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H71" t="n">
-        <v>81631.02</v>
+        <v>83930.92999999999</v>
       </c>
       <c r="I71" t="n">
         <v>83357.44749134463</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K71" t="n">
-        <v>3.2</v>
+        <v>0.47</v>
       </c>
       <c r="L71" t="n">
-        <v>0.75</v>
+        <v>1.83</v>
       </c>
       <c r="M71" t="n">
-        <v>0.66</v>
+        <v>4.52</v>
       </c>
       <c r="N71" t="n">
-        <v>1.42</v>
+        <v>2.54</v>
       </c>
       <c r="O71" t="n">
         <v>-0.95</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="72">
@@ -4524,22 +5387,22 @@
         <v>3.43</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46072.38541666666</v>
+        <v>46072.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>83037.57000000001</v>
+        <v>82348.17999999999</v>
       </c>
       <c r="I72" t="n">
         <v>82434.18897050526</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>16</v>
+        <v>16.16666666666667</v>
       </c>
       <c r="K72" t="n">
-        <v>-1.06</v>
+        <v>-1.89</v>
       </c>
       <c r="L72" t="n">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="M72" t="n">
         <v>0.86</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S72" t="b">
+        <v>0</v>
+      </c>
+      <c r="T72" t="n">
+        <v>1</v>
+      </c>
+      <c r="U72" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -4581,28 +5456,28 @@
         <v>2.65</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>74623.35000000001</v>
+        <v>77461.88</v>
       </c>
       <c r="I73" t="n">
         <v>75224.73352987957</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>47</v>
+        <v>47.83333333333334</v>
       </c>
       <c r="K73" t="n">
-        <v>9.380000000000001</v>
+        <v>5.93</v>
       </c>
       <c r="L73" t="n">
         <v>1.38</v>
       </c>
       <c r="M73" t="n">
-        <v>2.31</v>
+        <v>3.57</v>
       </c>
       <c r="N73" t="n">
-        <v>2.21</v>
+        <v>3.99</v>
       </c>
       <c r="O73" t="n">
         <v>-1.6</v>
@@ -4611,7 +5486,19 @@
         <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>3</v>
+      </c>
+      <c r="U73" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="74">
@@ -4638,19 +5525,19 @@
         <v>4.97</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46135.55208333334</v>
+        <v>46136.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>77611.25</v>
+        <v>76536.14</v>
       </c>
       <c r="I74" t="n">
         <v>77037.19000475771</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K74" t="n">
-        <v>0.19</v>
+        <v>-1.2</v>
       </c>
       <c r="L74" t="n">
         <v>2.06</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>3.66</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46185.38541666666</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="H75" t="n">
-        <v>74528.60000000001</v>
+        <v>75532.94</v>
       </c>
       <c r="I75" t="n">
         <v>75485.21978518464</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>49</v>
+        <v>49.16666666666666</v>
       </c>
       <c r="K75" t="n">
-        <v>2.62</v>
+        <v>1.31</v>
       </c>
       <c r="L75" t="n">
         <v>2.42</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>67</v>
+        <v>68</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>3.43</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H76" t="n">
-        <v>77587</v>
+        <v>76514.28</v>
       </c>
       <c r="I76" t="n">
         <v>77043.63835263639</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K76" t="n">
-        <v>2.72</v>
+        <v>1.3</v>
       </c>
       <c r="L76" t="n">
         <v>1.39</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2</v>
+      </c>
+      <c r="U76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -4809,25 +5732,25 @@
         <v>2.79</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46231.55208333334</v>
+        <v>46232.38541666666</v>
       </c>
       <c r="H77" t="n">
-        <v>76737.39999999999</v>
+        <v>77664.44</v>
       </c>
       <c r="I77" t="n">
         <v>77332.34288544276</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>20</v>
+        <v>20.83333333333333</v>
       </c>
       <c r="K77" t="n">
-        <v>-0.29</v>
+        <v>-1.5</v>
       </c>
       <c r="L77" t="n">
         <v>2.31</v>
       </c>
       <c r="M77" t="n">
-        <v>0.74</v>
+        <v>0.89</v>
       </c>
       <c r="N77" t="n">
         <v>1.29</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="n">
+        <v>2</v>
+      </c>
+      <c r="U77" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>2.06</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46251.55208333334</v>
+        <v>46252.38541666666</v>
       </c>
       <c r="H78" t="n">
-        <v>77728.16</v>
+        <v>77361.95</v>
       </c>
       <c r="I78" t="n">
         <v>77551.83006125348</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K78" t="n">
-        <v>0.08</v>
+        <v>-0.39</v>
       </c>
       <c r="L78" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M78" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="N78" t="n">
-        <v>0.58</v>
+        <v>0.63</v>
       </c>
       <c r="O78" t="n">
         <v>1.17</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S78" t="b">
+        <v>0</v>
+      </c>
+      <c r="T78" t="n">
+        <v>1</v>
+      </c>
+      <c r="U78" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -4923,19 +5870,19 @@
         <v>1.61</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>46309.55208333334</v>
+        <v>46310.38541666666</v>
       </c>
       <c r="H79" t="n">
-        <v>72781.89</v>
+        <v>74182.98</v>
       </c>
       <c r="I79" t="n">
         <v>73211.70795611724</v>
       </c>
       <c r="J79" s="2" t="n">
-        <v>57.16666666666666</v>
+        <v>58</v>
       </c>
       <c r="K79" t="n">
-        <v>5.92</v>
+        <v>4.11</v>
       </c>
       <c r="L79" t="n">
         <v>0.8100000000000001</v>
@@ -4944,7 +5891,7 @@
         <v>0.79</v>
       </c>
       <c r="N79" t="n">
-        <v>1.54</v>
+        <v>2.11</v>
       </c>
       <c r="O79" t="n">
         <v>-0.63</v>
@@ -4953,7 +5900,19 @@
         <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>80</v>
+        <v>81</v>
+      </c>
+      <c r="R79" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="n">
+        <v>3</v>
+      </c>
+      <c r="U79" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="80">
@@ -4980,22 +5939,22 @@
         <v>3.54</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>46317.55208333334</v>
+        <v>46318.38541666666</v>
       </c>
       <c r="H80" t="n">
-        <v>73249.39</v>
+        <v>72552.73</v>
       </c>
       <c r="I80" t="n">
         <v>72784.68378889443</v>
       </c>
       <c r="J80" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K80" t="n">
-        <v>-1.26</v>
+        <v>-2.2</v>
       </c>
       <c r="L80" t="n">
-        <v>1.73</v>
+        <v>2.33</v>
       </c>
       <c r="M80" t="n">
         <v>0.5</v>
@@ -5010,7 +5969,19 @@
         <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R80" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S80" t="b">
+        <v>0</v>
+      </c>
+      <c r="T80" t="n">
+        <v>1</v>
+      </c>
+      <c r="U80" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="81">
@@ -5061,6 +6032,14 @@
       <c r="Q81" t="n">
         <v>8</v>
       </c>
+      <c r="R81" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S81" t="b">
+        <v>1</v>
+      </c>
+      <c r="T81" t="inlineStr"/>
+      <c r="U81" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7163,7 +8142,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22.1</v>
       </c>
     </row>
     <row r="6">
@@ -7173,7 +8152,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -7183,7 +8162,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>63.2</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8">
@@ -7193,7 +8172,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -7203,7 +8182,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25.9</v>
+        <v>26.6</v>
       </c>
     </row>
     <row r="10">
@@ -7213,7 +8192,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>47.4</v>
+        <v>48.2</v>
       </c>
     </row>
     <row r="11">
@@ -7253,7 +8232,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.41</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="15">
@@ -7263,7 +8242,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.68</v>
+        <v>0.6</v>
       </c>
     </row>
     <row r="16">
@@ -7273,7 +8252,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.12</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="17">
@@ -7283,7 +8262,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>11.61</v>
+        <v>10.48</v>
       </c>
     </row>
     <row r="18">
@@ -7293,7 +8272,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>62</v>
+        <v>44.3</v>
       </c>
     </row>
     <row r="19">
@@ -7303,7 +8282,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.3</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="20">
@@ -7313,7 +8292,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.06</v>
+        <v>1.34</v>
       </c>
     </row>
     <row r="21">
@@ -7323,7 +8302,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5.55</v>
+        <v>7.91</v>
       </c>
     </row>
     <row r="22">
@@ -7333,7 +8312,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -7353,7 +8332,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.68</v>
+        <v>0.96</v>
       </c>
     </row>
     <row r="25">
@@ -7363,7 +8342,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>2.31</v>
+        <v>4.52</v>
       </c>
     </row>
     <row r="26">
@@ -7373,7 +8352,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1.21</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="27">
@@ -7383,7 +8362,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3.24</v>
+        <v>5.26</v>
       </c>
     </row>
     <row r="28">
@@ -7393,7 +8372,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
